--- a/신고신저가_20260806.xlsx
+++ b/신고신저가_20260806.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,56 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 지수는 쉬어가는데(나스닥-0.8%) 신고가 120건으로 오히려 확대 — 대형테크 밖 실적주로 온기가 번지는 폭 넓어짐 국면으로 추정. 중화권은 소재·반도체 쏠림 반등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/5): 다우+0.5%·S&amp;P-0.2%·나스닥-0.8%. 신고120(NEW46)/신저18(NEW11). 강세=금융(순강도+30, 신고32·12MF PER15.4·표본160)·테크서비스(+19, PER22.6)·헬스(+9, XLV+1.3%)·소재(XLB+1.2%), 약세=유틸리티(신저5, XLU-1.0%)·에너지(XLE-2.1%). 쇼피파이+17%·벤딩스푼스+16.8%·찰스리버+11.4%·다이나트레이스+11.3% 실적 랠리; 스포츠베팅 동반 붕괴(플러터-11.5% 미국수익 급감·가이던스 하향, 드래프트킹스-7.8%)·다비타-17%·RB글로벌-13.9%·뉴욕타임스-13.4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/5): 철강·비철ETF+7.0%(주간+18.9%)로 압도적 주도, 전기정밀+4.0%·정보통신+2.9%·은행+2.6%. 일본제철+4.0% 신고가(1분기 실적 상향수정). 반대편 다이킨-6.3% 신저가(서프라이즈 부재 차익실현)·카지마건설(가이던스 동결).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/5): 항셍+0.2%·항셍테크+1.0%. 신고8/신저0. 촹커실업+8.1%(상반기 순이익+17.5%·배당20%↑·5억달러 자사주)·캐세이퍼시픽+2.8%(상반기 순이익 65~75% 급증 예고).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/5): 상해+1.5%·CSI300+1.2%. 반도체ETF+6.6%·유색금속+5.2%·테크+4.2% 주도, 은행-1.2%·백주-0.9%로 자금 순환. 시부쾅예(구리·아연 광산)+7.4% 신고가(상반기 순이익+123%). 단 반도체는 1M-22.7% 낙폭 뒤 반등이라 되돌림 성격.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①미 실적시즌 후반 가이던스 톤(상향 랠리가 이어지는지) ②스포츠베팅 업종 훼손이 구조적인지 일회성인지 ③중국 반도체·유색 급등이 추세 전환인지 낙폭과대 반등인지 ④일본 철강 주간+18.9% 랠리의 근거 지속성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 美는 한국시간 8/6 새벽 마감분(현지 8/5). 日·홍콩·中은 8/5 마감 확정치. 중국A는 12MF 애널리스트 커버리지가 얇아 섹터 PER 인용 생략.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +763,19 @@
       <c r="C2" t="n">
         <v>7723.55</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.17</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>5.57</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>2.93</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>6.4</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>12.83</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +801,19 @@
       <c r="C3" t="n">
         <v>26363.44</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.83</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>7.86</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>2.11</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>13.43</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +839,19 @@
       <c r="C4" t="n">
         <v>6358.95</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>1.62</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>5.57</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-21.38</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-3.64</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>50.89</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +877,19 @@
       <c r="C5" t="n">
         <v>63957.53</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.32</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>2.55</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>7.47</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>27.05</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +915,19 @@
       <c r="C6" t="n">
         <v>3878.43</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>1.47</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-7.22</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.28</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +953,19 @@
       <c r="C7" t="n">
         <v>4658.15</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>1.24</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>1.26</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.61</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +991,19 @@
       <c r="C8" t="n">
         <v>25915.82</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>0.24</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.42</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>10.29</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>1.11</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1029,19 @@
       <c r="C9" t="n">
         <v>4933.07</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>0.97</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-10.57</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1160,7 @@
       <c r="F2" t="n">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1201,7 @@
       <c r="F3" t="n">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1242,7 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1283,7 @@
       <c r="F5" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1324,7 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1365,7 @@
       <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1406,7 @@
       <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1447,7 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1488,7 @@
       <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1529,7 @@
       <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1570,7 @@
       <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1611,7 @@
       <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1652,7 @@
       <c r="F14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1693,7 @@
       <c r="F15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1680,7 +1734,7 @@
       <c r="F16" t="n">
         <v>-1</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1775,7 @@
       <c r="F17" t="n">
         <v>-1</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1762,7 +1816,7 @@
       <c r="F18" t="n">
         <v>-5</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1978,7 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2019,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2058,7 @@
       <c r="F24" t="n">
         <v>-1</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2043,7 +2097,7 @@
       <c r="F25" t="n">
         <v>-1</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2638,7 +2692,7 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2679,7 +2733,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2720,7 +2774,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2761,7 +2815,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2802,7 +2856,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2843,7 +2897,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3362,7 +3416,7 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3403,7 +3457,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3442,7 +3496,7 @@
       <c r="F60" t="n">
         <v>-1</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4066,30 +4120,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4110,90 +4165,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4215,58 +4275,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1D-0.5%로 숨고르기, 다만 전자기술 순강도+10·테크서비스+19로 개별 신고가는 계속 확대</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>29.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4286,58 +4351,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.3% 당일 최강, 헬스테크 신고10건(찰스리버 실적 서프라이즈)으로 CRO·바이오 온기</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4357,58 +4427,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1D+0.2%지만 순강도+30(신고32)으로 전 섹터 1위, 12MF PER15.4 부담 낮은 폭 넓은 강세</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4428,58 +4503,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1D+0.3%, 소비내구재·유통 신고 지속(샤크닌자+8.3%)이나 베팅주 붕괴로 소비서비스는 혼조</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4499,58 +4579,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1D-1.0% 약세, 뉴욕타임스-13.4% 등 미디어 구독 성장둔화 우려가 지수 눌림</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4570,58 +4655,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1D보합, 생산재 신고9건으로 내부는 견조하나 산업서비스는 RB글로벌-13.9%로 약세 혼재</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4641,58 +4731,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1D보합·주간-2.3%로 소외 지속, IFF+8.9%(향료 실적)만 개별 강세</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4712,58 +4807,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1D-2.1%로 당일 최약, 에너지 신고·신저 모두 0으로 방향성 부재(유가 약세 추정)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4783,58 +4883,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1D-1.0%·1M-4.5%, 신저5건으로 유일한 명확한 약세 섹터(금리·실적 부담 추정)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4854,58 +4959,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.2%, 비에너지광물 신고4건 — 글로벌 금속 강세(중국 유색+5.2%, 일본 철강+7.0%)와 동조</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4925,58 +5035,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1D+0.1% 보합, 신고·신저 신호 없이 관망(리츠 개별 촉매 부재)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4996,58 +5111,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5067,58 +5183,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5138,58 +5255,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-9.5</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5209,58 +5327,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5280,58 +5399,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-6.9</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5351,58 +5471,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5422,58 +5543,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-13.2</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>49.4</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5493,58 +5615,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5564,58 +5687,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>35.8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5635,58 +5759,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5706,58 +5831,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5777,58 +5903,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-6.8</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5848,58 +5975,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-6.8</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5919,58 +6047,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5990,58 +6119,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>44.1</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6061,58 +6191,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6132,58 +6263,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-8.1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-6.2</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-12.4</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6203,58 +6335,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6274,58 +6407,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6345,56 +6479,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-10.2</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6412,58 +6547,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>1D+6.6% 당일 최강이나 1M-22.7% 낙폭 뒤 반등이라 되돌림 성격으로 추정</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-22.7</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>41.1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6483,58 +6623,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>1D+4.2%, 반도체 주도 낙폭과대 반등에 동조(1M-15.3%로 여전히 마이너스)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6554,58 +6699,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.6%, 테크 반등에 후행 동참하나 1M-16.4%로 회복 폭 제한적</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-16.4</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6625,56 +6775,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>1D+2.1%, 3M-23.8%의 깊은 조정에서 소재·배터리 금속 강세 힘입어 소폭 반등</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-23.8</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-11.1</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6692,58 +6847,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.8%, 3M-21.4% 조정 지속 중 기술적 반등 수준(신규 촉매 미확인)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-21.4</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-17.3</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6763,56 +6923,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.5%, 3M-22.3%로 여전히 부진하며 테크 순환매 온기만 일부 수취</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>-7.8</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.3</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-11.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6830,58 +6995,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1D-0.9%, 1M+12.1%로 앞서 오른 뒤 차익실현 — 자금이 테크·소재로 이동</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-18.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6901,58 +7071,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1D-1.2% 당일 최약, 방어주 자금 이탈로 위험선호 회복의 반대편</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6972,58 +7147,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>1D+5.2%·주간+7.6%, 시부쾅예 신고가(순이익+123%)로 금속가격 강세 실적 확인</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-13.8</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7043,58 +7223,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.8%지만 3M-17.9%, 부동산 정책 기대 없는 반등이라 지속성 낮게 추정</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-17.9</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-19.5</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7114,58 +7299,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>1D+0.5%, 지수 +1.5% 대비 부진 — 거래대금 증가에도 증권주 소외</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7185,58 +7375,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>1D+1.0%·1M+9.3%, 의약이 조용히 상승세 유지(헬스 신고1건)</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7256,58 +7451,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1D-0.7%, 백주와 함께 소비 차익실현 — 1M+7.0% 상승분 되돌림</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7319,7 +7519,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-2.1"/>
@@ -7331,7 +7531,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-8.1"/>
@@ -7343,7 +7543,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-22.7"/>
@@ -7355,7 +7555,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-23.8"/>
@@ -7367,7 +7567,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-19.5"/>
@@ -7379,7 +7579,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7391,7 +7591,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7403,7 +7603,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7415,7 +7615,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7427,7 +7627,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7439,7 +7639,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7553,7 +7753,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7606,15 +7806,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7662,10 +7862,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7712,14 +7912,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 팔란티어(AI 소프트웨어·데이터분석): 2분기 매출 93%↑에 연간 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7770,19 +7970,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 델(PC·서버·데이터센터 인프라): AI서버 수주 급증·실적 서프라이즈로 사상 최고가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7830,15 +8030,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7886,10 +8086,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7942,15 +8142,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7998,15 +8198,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8052,15 +8252,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8106,15 +8306,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8158,10 +8358,14 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>쇼피파이(이커머스 플랫폼): 2분기 실적 서프라이즈로 +17%, 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8214,14 +8418,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 이튼(전력관리·전기장비): Q2 EPS·매출 상회, 전력인프라 수주 급증·FY26 가이던스 상향, 에버코어 목표가 상향</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8270,15 +8474,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8320,10 +8524,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8372,10 +8576,10 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8424,15 +8628,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8480,10 +8684,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8532,14 +8736,14 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 엔브리지(캐나다 에너지 파이프라인): 개별 뉴스 없음, 에너지 섹터 약세(추정)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8590,14 +8794,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 스노우플레이크(클라우드 데이터플랫폼): 웰스파고 목표가 $320→$500 상향·AI에이전트 지출 가속 논거</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8648,10 +8852,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8704,15 +8908,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8756,10 +8960,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8806,10 +9010,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8862,10 +9066,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8914,10 +9118,10 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8966,10 +9170,10 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9018,10 +9222,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9070,15 +9274,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9122,10 +9326,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9174,15 +9378,15 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9226,10 +9430,10 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9276,15 +9480,15 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9328,10 +9532,10 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9382,15 +9586,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9434,10 +9638,10 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9490,10 +9694,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9546,10 +9750,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9598,10 +9802,10 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9650,10 +9854,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9706,10 +9910,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9762,10 +9966,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9818,10 +10022,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9870,14 +10074,14 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 톰슨로이터(법률·세무 정보서비스): 8/5 실적 발표 앞둔 기대·정보서비스주 동반 강세(추정)</t>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>톰슨로이터(법률·세무·뉴스 정보서비스): 2분기 발표 후 -9.7% 급락, 고점권 이탈</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9926,10 +10130,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9982,10 +10186,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10034,15 +10238,15 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10086,15 +10290,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10142,10 +10346,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10194,10 +10398,10 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10250,10 +10454,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10302,14 +10506,14 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>(전일) 인거솔랜드(산업용 압축기·펌프): Q2 실적·가이던스 상향, Baird 목표가 상향에 신고가</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10358,10 +10562,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10414,10 +10618,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10466,10 +10670,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10518,10 +10722,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10574,15 +10778,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>테레다인(계측·이미징 장비): 신규 촉매 미확인, 실적 호조 후 고점 유지</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10628,10 +10836,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10680,15 +10888,15 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10732,10 +10940,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10788,10 +10996,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10840,15 +11048,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10892,15 +11100,15 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10944,15 +11152,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11000,15 +11208,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11054,10 +11262,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>벤딩스푼스(앱 인수·운영 이탈리아 테크): +16.8% 급등, 촉매 미확인(상장 초기 변동성 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11106,10 +11318,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11162,15 +11374,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11214,10 +11426,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11270,10 +11482,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>샤크닌자(소형가전): 2분기 서프라이즈·연간 가이던스 상향으로 +8.3%</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11326,10 +11542,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11378,19 +11594,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>(전일) 아르시스(방산·항공우주 부품): 2분기 매출 25%↑·EBITDA 38%↑, 연간 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11438,10 +11654,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11490,15 +11706,15 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11546,15 +11762,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11602,15 +11818,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11658,10 +11874,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11710,15 +11926,15 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11766,10 +11982,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>IFF(향료·향미 소재): 2분기 실적 호조로 +8.9%, 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11816,10 +12036,10 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11868,15 +12088,15 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11924,15 +12144,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11980,15 +12200,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12036,10 +12256,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12088,10 +12308,10 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="7" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12140,10 +12360,10 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="7" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12196,15 +12416,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12248,15 +12468,15 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="7" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12298,10 +12518,10 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12350,15 +12570,15 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="7" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12402,15 +12622,15 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" s="7" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12454,15 +12674,15 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="7" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12510,10 +12730,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N93" s="7" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12562,19 +12782,19 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="7" t="inlineStr">
+      <c r="N94" s="10" t="inlineStr">
         <is>
           <t>(전일) 블루아울(사모대출·대안자산운용): Q2 매출 $754M 컨센 9.6% 상회, 英 스파이어헬스케어 병원 13억파운드 인수 등 딜 발표로 급등</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12618,15 +12838,15 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" s="7" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12670,10 +12890,14 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="7" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>RB글로벌(산업장비 경매 마켓플레이스): 실적 실망으로 -13.9%, 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12726,10 +12950,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N97" s="7" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12782,14 +13006,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N98" s="7" t="inlineStr">
+      <c r="N98" s="10" t="inlineStr">
         <is>
           <t>(전일) 지브라테크(바코드스캐너·산업용 모바일기기): 2분기 실적 컨센 상회로 급등</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12836,10 +13060,10 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" s="7" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12892,10 +13116,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12948,14 +13172,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N101" s="7" t="inlineStr">
+      <c r="N101" s="10" t="inlineStr">
         <is>
           <t>(전일) 존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13004,10 +13228,10 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="7" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13060,15 +13284,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13112,15 +13336,15 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" s="7" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13164,15 +13388,15 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="7" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13216,10 +13440,10 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" s="7" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13266,10 +13490,10 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="7" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13318,15 +13542,15 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" s="7" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13372,10 +13596,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N109" s="7" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr">
+        <is>
+          <t>플러터(온라인 스포츠베팅, 팬듀얼): 2분기 미국 수익 급감·가이던스 하향으로 -11.5%</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13428,10 +13656,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N110" s="7" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13476,14 +13704,14 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" s="7" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>(전일) 유니티소프트웨어(게임엔진·3D툴): Q2 실적(8/5) 기대·전략매출 35% 성장 확인, 7/31 급락분 반등에 나스닥 강세 수혜</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13532,15 +13760,15 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="7" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13584,15 +13812,15 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" s="7" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13634,10 +13862,10 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="7" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13686,15 +13914,15 @@
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" s="7" t="inlineStr"/>
+      <c r="N115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13742,15 +13970,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N116" s="7" t="inlineStr"/>
+      <c r="N116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13798,15 +14026,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N117" s="7" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>다이나트레이스(앱 성능 모니터링 SW): 1QFY27 ARR +17% 호조로 +11%</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13850,10 +14082,10 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" s="7" t="inlineStr"/>
+      <c r="N118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13902,10 +14134,10 @@
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" s="7" t="inlineStr"/>
+      <c r="N119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13956,15 +14188,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N120" s="7" t="inlineStr"/>
+      <c r="N120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14004,10 +14236,10 @@
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" s="7" t="inlineStr"/>
+      <c r="N121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14058,15 +14290,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N122" s="7" t="inlineStr"/>
+      <c r="N122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14114,10 +14346,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N123" s="7" t="inlineStr"/>
+      <c r="N123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14170,15 +14402,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N124" s="7" t="inlineStr"/>
+      <c r="N124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14224,10 +14456,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N125" s="7" t="inlineStr"/>
+      <c r="N125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14280,10 +14512,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N126" s="7" t="inlineStr"/>
+      <c r="N126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14336,10 +14568,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N127" s="7" t="inlineStr"/>
+      <c r="N127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14386,15 +14618,15 @@
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" s="7" t="inlineStr"/>
+      <c r="N128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14438,15 +14670,15 @@
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" s="7" t="inlineStr"/>
+      <c r="N129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14492,10 +14724,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N130" s="7" t="inlineStr"/>
+      <c r="N130" s="10" t="inlineStr">
+        <is>
+          <t>찰스리버랩스(신약 전임상 CRO): 2분기 서프라이즈·가이던스 상향, 바이오텍 수요 회복</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14548,10 +14784,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N131" s="7" t="inlineStr"/>
+      <c r="N131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14600,19 +14836,19 @@
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" s="7" t="inlineStr">
+      <c r="N132" s="10" t="inlineStr">
         <is>
           <t>(전일) 가트너(IT 리서치·자문): 2분기 서프라이즈·26년 EPS 가이던스 13.25→14달러 상향</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14656,15 +14892,15 @@
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" s="7" t="inlineStr"/>
+      <c r="N133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14706,10 +14942,14 @@
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" s="7" t="inlineStr"/>
+      <c r="N134" s="10" t="inlineStr">
+        <is>
+          <t>다비타(신장투석 체인): 2분기 EPS 상회에도 가이던스 우려로 -17%, 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14758,15 +14998,15 @@
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" s="7" t="inlineStr"/>
+      <c r="N135" s="10" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14810,15 +15050,19 @@
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" s="7" t="inlineStr"/>
+      <c r="N136" s="10" t="inlineStr">
+        <is>
+          <t>드래프트킹스(온라인 스포츠베팅): 플러터 실적 쇼크 여파로 동반 -7.8%</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14862,10 +15106,14 @@
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" s="7" t="inlineStr"/>
+      <c r="N137" s="10" t="inlineStr">
+        <is>
+          <t>뉴욕타임스(언론·디지털 구독): 2분기 현금흐름 부진·성장 둔화 우려로 -13.4%</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14918,19 +15166,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N138" s="7" t="inlineStr">
+      <c r="N138" s="10" t="inlineStr">
         <is>
           <t>(전일) 사우스스테이트은행(미 남동부 지역은행): 개별 뉴스 없음, 은행주 전반 강세 동반(추정)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14974,7 +15222,7 @@
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" s="7" t="inlineStr"/>
+      <c r="N139" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N139"/>
@@ -15080,7 +15328,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15133,19 +15381,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 키엔스(FA 센서·측정기기): 엔저에 기계·반도체 반등, 신고가 랠리 연장</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15187,15 +15435,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>다이킨공업(공조기기): 1분기 무난했으나 서프라이즈 부재로 차익실현 -6.3%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15239,15 +15491,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>일본제철(고로 철강): 1분기 실적 상향수정으로 +4%, 철강·비철 섹터 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15289,7 +15545,11 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>카지마건설(종합건설): 1분기 경상이익 상회에도 연간 가이던스 동결로 하락</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N5"/>
@@ -15395,7 +15655,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15444,19 +15704,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 텐센트(인터넷·게임·소셜): 특별한 뉴스 없음, 업종 순환매 속 소폭 조정</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15504,10 +15764,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>매뉴라이프(캐나다계 보험·자산운용): 신규 촉매 미확인, 금융 섹터 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15558,19 +15822,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 야오밍캉더(신약 위탁개발 CRO): 상반기 실적 서프라이즈·연간 가이던스 대폭 상향</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15618,10 +15882,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>촹커실업(밀워키·라이오비 전동공구): 상반기 순이익 +17.5%·배당 20%↑·5억달러 자사주로 +8.1%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15670,14 +15938,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 야오밍바이오(바이오의약 CDMO): 야오밍캉더 실적발 위탁개발 업종 훈풍에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15724,14 +15992,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 프라다(이탈리아 명품패션): 7/30 상반기 매출 +16%(불변환율)·Q2 유기성장 +7% 가속 확인 후 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15780,19 +16048,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 지투글로벌익스프레스(글로벌 택배물류): Q2 소포량 +24%·일평균 1억건 돌파, 6월 HK$20억 자사주매입 계획이 지지</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15838,7 +16106,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>캐세이퍼시픽(홍콩 국적 항공사): 상반기 순이익 65~75% 급증 전망 공시로 강세</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N9"/>
@@ -15944,12 +16216,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15993,10 +16265,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>리쉰정미(애플 공급망 전자부품·조립): 신규 촉매 없이 소비전자 소외로 신저가 이탈</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16047,19 +16323,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 야오밍캉더(신약 위탁개발 CRO): 상반기 실적·연간 가이던스 대폭 상향으로 상한가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16101,7 +16377,11 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>시부쾅예(구리·아연·몰리브덴 광산): 상반기 순이익 +123% 사상 최고, 유색금속 강세로 +7.4%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N4"/>
